--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_927_Colombia_Caribbean.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_927_Colombia_Caribbean.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rbcf159b9047246e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R590476fe5d304204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0eeb0d7092744c60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R732fc24cabc34b3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rff8c7b9011754445"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf7cb8c0fe2f74b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5ea25ca9a58443f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rda01bda3ae6a4993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4126524561574805"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R9d0dab14d7104dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd6c934f8c28d4c64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R676dfc7e25a446ad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ927CommercialTable" displayName="EEZ927CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ927CommercialTable" displayName="EEZ927CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ927FunctionalTable" displayName="EEZ927FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ927FunctionalTable" displayName="EEZ927FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ927ValidationTable" displayName="EEZ927ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ927ValidationTable" displayName="EEZ927ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6657,7 +6611,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8ff0c9cb5484181"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b8bf54a022948d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6667,20 +6621,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6688,444 +6632,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>690.5100000002</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.9459745695211526</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>88.30281924457971</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>690.5100000002</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>107.03423388634013</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$90,A2,'Species'!$U$2:$U$90))</x:f>
-        <x:v>73908.20884087813</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.9459745695211526</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>88.30281924457971</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>60973.979716592396</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>12934.229124285732</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.212127028355442</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.21212702835544187</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>434.2340766759</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.1453565691468155</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1397.5152932603187</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>434.2340766759</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2363.6064461582323</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$90,A3,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1026358.4627727253</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.1453565691468155</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1397.5152932603187</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>606848.7630093441</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>419509.69976338116</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.6912920077204172</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.6912920077204172</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>409.8678312741</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.1840805190611645</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>15.278492982808562</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>409.8678312741</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>15.303386614214338</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$90,A4,'Species'!$U$2:$U$90))</x:f>
-        <x:v>6272.365882717123</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.1840805190611645</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>15.278492982808562</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>6262.1627840003</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>10.203098716822751</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0016293250540997</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0016293250540997534</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3725.9915050503996</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.491508438574978</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>310.1047642967767</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3725.9915050503996</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>445.85669952212294</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$90,A5,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1661258.2748892386</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.491508438574978</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>310.1047642967767</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1155447.7174454464</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>505810.55744379223</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.437761527247704</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.43776152724770406</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>14144.024844271698</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.7767313410437326</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>598.0415260749992</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>14144.024844271698</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>867.3577789487425</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$90,A6,'Species'!$U$2:$U$90))</x:f>
-        <x:v>12267929.974323334</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.7767313410437326</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>598.0415260749992</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>8458714.202710949</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3809215.7716123853</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.4503303552201305</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.4503303552201306</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>530.6596122048</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.295728902177672</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>197.57359497386602</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>530.6596122048</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>491.8293248752657</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$90,A7,'Species'!$U$2:$U$90))</x:f>
-        <x:v>260993.9588092571</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.295728902177672</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>197.57359497386602</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>104844.32729073998</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>156149.63151851713</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>2.4893474502011377</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>1.4893474502011375</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>408.82419446939997</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.37648225048125</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2379.4810501085376</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>408.82419446939997</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2472.35034690879</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$90,A8,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1010756.6390211276</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.37648225048125</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2379.4810501085376</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>972789.4235658249</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>37967.215455302736</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.039029223114013</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.039029223114013065</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5987a04afbc424c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53e4457a2b5648a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7135,20 +6790,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7156,984 +6801,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>53.1362730775</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.018923335074864</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1044.5358136347204</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>53.1362730775</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1151.5101772309158</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$90,A2,'Species'!$U$2:$U$90))</x:f>
-        <x:v>61186.95922886237</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.018923335074864</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1044.5358136347204</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>55502.74023252315</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>5684.218996339216</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.102413303785106</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.10241330378510595</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>496.4720704672</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.67</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>467.73514128719813</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>496.4720704672</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>467.73514128719813</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$90,A3,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>232217.4340251236</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.67</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>467.73514128719813</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>232217.4340251236</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>681.7753368403</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.355238930459665</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2265.890561916684</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>681.7753368403</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2332.0666832993807</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$90,A4,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1589945.5485404767</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.355238930459665</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2265.890561916684</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1544828.301094004</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>45117.24744647276</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.029205347555144</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.029205347555143826</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>919.6676136024</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.225612859574272</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1681.1747537682918</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>919.6676136024</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2080.834081322767</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$90,A5,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1913675.7138726513</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.225612859574272</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1681.1747537682918</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1546121.9738466875</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>367553.74002596387</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2377262248666614</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.2377262248666613</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>437.15999999999997</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.099971406350078</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>125.88425277396585</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>437.15999999999997</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>218.81230823049344</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$90,A6,'Species'!$U$2:$U$90))</x:f>
-        <x:v>95655.98866604251</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.099971406350078</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>125.88425277396585</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>55031.55994266691</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>40624.428723375604</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.738202383608588</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.738202383608588</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1226.6047202408001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.645063099436144</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>441.63460858866523</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1226.6047202408001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>476.7342505826185</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$90,A7,'Species'!$U$2:$U$90))</x:f>
-        <x:v>584764.4820651002</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.645063099436144</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>441.63460858866523</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>541711.095516555</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>43053.38654854521</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.079476656293132</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.07947665629313194</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>93.4996122048</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.210998440285961</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1625.542917806948</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>93.4996122048</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1768.3278705056127</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$90,A8,'Species'!$U$2:$U$90))</x:f>
-        <x:v>165337.9701432146</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.210998440285961</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1625.542917806948</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>151987.63243720873</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>13350.33770600587</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0878383161308953</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.08783831613089539</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>200.7500000002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>200.7500000002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$90,A9,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>31816.730838688567</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>31816.730838688567</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>148.99</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.873594872139069</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>747.4719024715532</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>148.99</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>913.5367143560115</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$90,A10,'Species'!$U$2:$U$90))</x:f>
-        <x:v>136107.83507190217</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.873594872139069</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>747.4719024715532</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>111365.83874923672</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>24741.99632266545</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2221686344802483</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.22216863448024834</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5555.749588402701</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.4482338680348885</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>280.69447737514656</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5555.749588402701</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>410.22589540350765</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$90,A11,'Species'!$U$2:$U$90))</x:f>
-        <x:v>2279112.349540167</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.4482338680348885</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>280.69447737514656</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1559468.2271438818</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>719644.1223962852</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.4614676399751287</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.46146763997512874</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2202.3615387583</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.817273715438044</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>656.5589342268012</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2202.3615387583</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>875.3328475769072</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$90,A12,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1927799.3971151616</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.817273715438044</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>656.5589342268012</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1445980.1446692473</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>481819.2524459143</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.333212910441537</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.3332129104415368</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>6623.582961657799</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.862859851397911</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>729.2221493163934</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>6623.582961657799</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>932.0830602717841</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$90,A13,'Species'!$U$2:$U$90))</x:f>
-        <x:v>6173729.476866049</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.862859851397911</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>729.2221493163934</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>4830063.403475543</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1343666.0733905062</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2781880818424975</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.2781880818424975</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>409.8678312741</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.1840805190611645</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>15.278492982808562</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>409.8678312741</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>15.303386614214338</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$90,A14,'Species'!$U$2:$U$90))</x:f>
-        <x:v>6272.365882717123</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.1840805190611645</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>15.278492982808562</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>6262.1627840003</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>10.203098716822751</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0016293250540997</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.0016293250540997534</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>489.76</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.841850906566482</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>69.47857564713074</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>489.76</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>85.94307007960953</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$90,A15,'Species'!$U$2:$U$90))</x:f>
-        <x:v>42091.478002189564</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.841850906566482</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>69.47857564713074</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>34027.827208938754</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>8063.65079325081</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2369722504977507</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.23697225049775067</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>356.6104407445</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.03</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>107.1519305237606</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>356.6104407445</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>107.15193052376061</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$90,A16,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>38211.497170702314</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.03</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>38211.497170702314</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>442.3540766759</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>4.128737539891529</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>1345.0472469261395</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>442.3540766759</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>2323.4092579612116</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$90,A17,'Species'!$U$2:$U$90))</x:f>
-        <x:v>1027769.5570456698</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>4.128737539891529</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>1345.0472469261395</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>594987.1329994737</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>432782.42404619604</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.7273811483358226</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.7273811483358227</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>5.77</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.49</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>309.0295432513592</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>5.77</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>309.0295432513592</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$90,A18,'Species'!$U$2:$U$90))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1783.1004645603425</x:v>
       </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.49</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>309.0295432513592</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>1783.1004645603425</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbf16491dbb14349"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd5a359042c449a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8308,7 +7314,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8407,7 +7413,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>16307477.88453928</x:v>
+        <x:v>11365880.576522898</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8421,7 +7427,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>16307477.88453928</x:v>
+        <x:v>12781366.802599043</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8435,7 +7441,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-4941597.30801638</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8449,7 +7455,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-3526111.0819402356</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8460,9 +7466,9 @@
         <x:v>EEZ_927</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8474,47 +7480,19 @@
         <x:v>EEZ_927</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_927</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_927</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07a7f658db1c4a5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R340461646e6b4ac8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8561,7 +7539,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
